--- a/artfynd/A 26987-2026 artfynd.xlsx
+++ b/artfynd/A 26987-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103825069</v>
+        <v>103825070</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696717.7975337679</v>
+        <v>696678</v>
       </c>
       <c r="R2" t="n">
-        <v>6363919.437056816</v>
+        <v>6363959</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103825063</v>
+        <v>103825066</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696838.4656315831</v>
+        <v>696776</v>
       </c>
       <c r="R3" t="n">
-        <v>6363863.145626291</v>
+        <v>6363873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103825061</v>
+        <v>103825063</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696838.4656315831</v>
+        <v>696838</v>
       </c>
       <c r="R4" t="n">
-        <v>6363863.145626291</v>
+        <v>6363863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103825065</v>
+        <v>103825069</v>
       </c>
       <c r="B5" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696776.3012803567</v>
+        <v>696718</v>
       </c>
       <c r="R5" t="n">
-        <v>6363873.111888373</v>
+        <v>6363920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103825066</v>
+        <v>103825061</v>
       </c>
       <c r="B6" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696776.3012803567</v>
+        <v>696838</v>
       </c>
       <c r="R6" t="n">
-        <v>6363873.111888373</v>
+        <v>6363863</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,53 +1180,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103825070</v>
+        <v>69261934</v>
       </c>
       <c r="B7" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>449</v>
+        <v>221849</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hunninge, Gtl</t>
+          <t>Klintebys, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696678.0122644885</v>
+        <v>696807</v>
       </c>
       <c r="R7" t="n">
-        <v>6363959.103215847</v>
+        <v>6363738</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,15 +1265,205 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>69261574</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klintebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>696824</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6363737</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-07-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-07-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103825065</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hunninge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>696776</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6363873</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 26987-2026 artfynd.xlsx
+++ b/artfynd/A 26987-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103825070</v>
+        <v>134747118</v>
       </c>
       <c r="B2" t="n">
-        <v>87368</v>
+        <v>99088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>449</v>
+        <v>290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Röd skogslilja</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cephalanthera rubra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hunninge, Gtl</t>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696678</v>
+        <v>696755</v>
       </c>
       <c r="R2" t="n">
-        <v>6363959</v>
+        <v>6363887</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fem blommor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,52 +775,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd..</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103825066</v>
+        <v>103825070</v>
       </c>
       <c r="B3" t="n">
-        <v>87170</v>
+        <v>87368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696776</v>
+        <v>696678</v>
       </c>
       <c r="R3" t="n">
-        <v>6363873</v>
+        <v>6363959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103825063</v>
+        <v>103825066</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>87170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696838</v>
+        <v>696776</v>
       </c>
       <c r="R4" t="n">
-        <v>6363863</v>
+        <v>6363873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103825069</v>
+        <v>103825063</v>
       </c>
       <c r="B5" t="n">
         <v>92869</v>
@@ -1013,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696718</v>
+        <v>696838</v>
       </c>
       <c r="R5" t="n">
-        <v>6363920</v>
+        <v>6363863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103825061</v>
+        <v>103825069</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696838</v>
+        <v>696718</v>
       </c>
       <c r="R6" t="n">
-        <v>6363863</v>
+        <v>6363920</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,48 +1200,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69261934</v>
+        <v>103825061</v>
       </c>
       <c r="B7" t="n">
-        <v>107517</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221849</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klintebys, Gtl</t>
+          <t>Hunninge, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696807</v>
+        <v>696838</v>
       </c>
       <c r="R7" t="n">
-        <v>6363738</v>
+        <v>6363863</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,12 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-07-25</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-07-25</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,56 +1285,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69261574</v>
+        <v>134747325</v>
       </c>
       <c r="B8" t="n">
-        <v>104641</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224416</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Klintebys, Gtl</t>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696824</v>
+        <v>696788</v>
       </c>
       <c r="R8" t="n">
-        <v>6363737</v>
+        <v>6363820</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1338,12 +1371,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-07-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-07-25</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosök av spillkråka idöd stående gran och i en låga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,64 +1392,74 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, äldre, med enstaka lövträd.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103825065</v>
+        <v>134747326</v>
       </c>
       <c r="B9" t="n">
-        <v>87346</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hunninge, Gtl</t>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696776</v>
+        <v>696843</v>
       </c>
       <c r="R9" t="n">
-        <v>6363873</v>
+        <v>6363827</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1435,12 +1483,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosök av spillkråka vid foten av 2 döda granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,19 +1504,5029 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, äldre, med enstaka lövträd.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134747216</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>696775</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6364019</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134747217</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>696778</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6364000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134747218</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>696775</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6363981</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134747220</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>696750</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6363946</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr, fuktigt.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134747222</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>696771</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6363914</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134747223</v>
+      </c>
+      <c r="B15" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>696763</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6363863</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134747224</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>696771</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6363869</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134747225</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>696755</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6363887</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134747226</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>696747</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6363932</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134747227</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>696730</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6363922</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Märkligt mitt i skog. Dock en mindre grop med vatten mot N och fuktigare skog mot V.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134747229</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>696685</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6363907</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134747230</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>696659</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6363900</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134747231</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>696801</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6363791</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134747232</v>
+      </c>
+      <c r="B23" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>696829</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6363790</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr, i vildapel.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134747235</v>
+      </c>
+      <c r="B24" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>696839</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6363831</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134747236</v>
+      </c>
+      <c r="B25" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696847</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6363837</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134747237</v>
+      </c>
+      <c r="B26" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>696802</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6363932</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134747238</v>
+      </c>
+      <c r="B27" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>696800</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6363926</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, fuktig glänta med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134747239</v>
+      </c>
+      <c r="B28" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>696786</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6363937</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, fuktig glänta med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134747240</v>
+      </c>
+      <c r="B29" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>696779</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6363952</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Eventuellt 2 ex.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, fuktig glänta med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134747241</v>
+      </c>
+      <c r="B30" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>696767</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6363967</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarskog frisk till fuktig.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134747242</v>
+      </c>
+      <c r="B31" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>696782</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6363980</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarskog frisk till fuktig.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134747243</v>
+      </c>
+      <c r="B32" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>696790</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6364000</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarskog frisk till fuktig.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134747296</v>
+      </c>
+      <c r="B33" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>696768</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6363964</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134747234</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5497</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>696823</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6363829</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Tall angripen.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med gott om lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134747332</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58460</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102625</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Halsbandsflugsnappare</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ficedula albicollis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Temminck, 1795)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>696804</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6363839</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Förmodat bo i björk.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, äldre, med enstaka lövträd.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134747321</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>696747</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6363932</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ivrigt sjungande.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, äldre, med enstaka lövträd.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134747113</v>
+      </c>
+      <c r="B37" t="n">
+        <v>111471</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>696763</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6363863</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134747095</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99173</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>696764</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6364035</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134747109</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99173</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>696781</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6363857</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134747099</v>
+      </c>
+      <c r="B40" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>696775</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6364019</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134747102</v>
+      </c>
+      <c r="B41" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>696768</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6363964</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134747107</v>
+      </c>
+      <c r="B42" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>696774</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6363894</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134747115</v>
+      </c>
+      <c r="B43" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>696771</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6363869</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134747119</v>
+      </c>
+      <c r="B44" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>696747</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6363932</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134747128</v>
+      </c>
+      <c r="B45" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>696692</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6363863</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134747150</v>
+      </c>
+      <c r="B46" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>696829</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6363795</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, kant av glänta.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134747169</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>696812</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6363903</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd..</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134747153</v>
+      </c>
+      <c r="B48" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>696825</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6363812</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd..</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>69261934</v>
+      </c>
+      <c r="B49" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Klintebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>696807</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6363738</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2017-07-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2017-07-25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134747093</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99880</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>696759</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6364062</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikt spridd.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkgräsmyr i vinterfuktig glänta.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134747112</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:4 (2) A 26987-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>696763</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6363863</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarskog, äldre med grova träd, glänta med örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>69261574</v>
+      </c>
+      <c r="B52" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Klintebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>696824</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6363737</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2017-07-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2017-07-25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>103825065</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hunninge, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>696776</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6363873</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX53" t="inlineStr">
         <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY53" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 26987-2026 artfynd.xlsx
+++ b/artfynd/A 26987-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103825070</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103825066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103825063</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103825069</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103825061</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747325</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747326</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747216</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747217</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747218</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2006,6 +2066,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747220</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2127,6 +2192,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747222</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2248,6 +2318,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747223</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2369,6 +2444,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747224</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2490,6 +2570,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747225</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2611,6 +2696,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747226</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2737,6 +2827,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747227</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2858,6 +2953,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747229</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2979,6 +3079,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747230</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3100,6 +3205,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747231</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3221,6 +3331,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747232</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3342,6 +3457,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747235</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3463,6 +3583,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747236</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3584,6 +3709,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747237</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3705,6 +3835,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747238</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3826,6 +3961,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747239</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3952,6 +4092,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747240</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4073,6 +4218,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747241</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4194,6 +4344,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747242</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4315,6 +4470,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747243</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4436,6 +4596,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747296</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4543,6 +4708,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747234</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4664,6 +4834,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747332</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4780,6 +4955,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747321</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4891,6 +5071,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747113</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5002,6 +5187,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747095</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5113,6 +5303,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747109</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5215,6 +5410,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747099</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5317,6 +5517,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747102</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5419,6 +5624,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747107</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5521,6 +5731,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747115</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5623,6 +5838,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747119</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5725,6 +5945,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747128</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5827,6 +6052,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747150</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5929,6 +6159,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747169</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6031,6 +6266,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747153</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6128,6 +6368,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69261934</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6235,6 +6480,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747093</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6337,6 +6587,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134747112</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6430,6 +6685,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69261574</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6531,8 +6791,67 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103825065</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>